--- a/data/review/gold_A.xlsx
+++ b/data/review/gold_A.xlsx
@@ -712,7 +712,8 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Thông tư số 07/2024/TT-BKHCN Sửa đổi, bổ sung một số điều tại các văn bản quy phạm pháp luật thuộc thẩm quyền của Bộ trưởng Bộ Khoa học và C (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=170642)</t>
+          <t>• 07/2024/TT-BKHCN — sửa đổi, bổ sung — hiệu lực 22/11/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=170642</t>
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr"/>
@@ -754,7 +755,8 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 88/2025/NĐ-CP Quy định chi tiết và hướng dẫn một số điều của Nghị quyết số 193/2025/QH15 ngày 19 tháng 02 năm 2025 của Quốc hội (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=177799)</t>
+          <t>• 88/2025/NĐ-CP — bãi bỏ — hiệu lực 13/04/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=177799</t>
         </is>
       </c>
       <c r="H3" s="8" t="inlineStr"/>
@@ -796,7 +798,12 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 56/2019/TT-BTC Sửa đổi, bổ sung một số điều của Thông tư số 49/2015/TT-BTC ngày 14 tháng 4 năm 2015 quy định thủ tục hải quan đố (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=137595) | hợp nhất: Văn bản hợp nhất số 01/VBHN-BTC Thông tư quy định thủ tục hải quan đối với hàng hóa xuất khẩu, nhập khẩu, quá cảnh gửi qua dịch vụ chuyển ph (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=140467) | sửa đổi, bổ sung: Thông tư số 56/2019/TT-BTC Sửa đổi, bổ sung một số điều của Thông tư số 49/2015/TT-BTC ngày 14 tháng 4 năm 2015 quy định thủ tục hải quan đố (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=137595) | sửa đổi, bổ sung: Thông tư số 29/2025/TT-BTC Sửa đổi, bổ sung một số điều của Thông tư số 191/2015/TT-BTC ngày 24 tháng 11 năm 2015 quy định thủ tục hải quan  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178369)</t>
+          <t>• 56/2019/TT-BTC — bãi bỏ, sửa đổi, bổ sung — hiệu lực 15/10/2019
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=137595
+• 29/2025/TT-BTC — sửa đổi, bổ sung — hiệu lực 09/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178369
+• 01/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=140467</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr"/>
@@ -838,7 +845,10 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 10/VBHN-BTC Hướng dẫn việc chuyển giao quyền đại diện chủ sở hữu nhà nước tại Tổng công ty Đầu tư và Kinh doanh vốn Nhà  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=157328) | sửa đổi, bổ sung: Thông tư số 119/2021/TT-BTC Sửa đổi, bổ sung một số Điều của Thông tư số 83/2018/TT-BTC ngày 30 tháng 08 năm 2018 của Bộ trưởng Bộ Tài chính (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152520)</t>
+          <t>• 119/2021/TT-BTC — sửa đổi, bổ sung — hiệu lực 15/02/2022
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152520
+• 10/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=157328</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr"/>
@@ -880,7 +890,8 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Nghị định số 84/2026/NĐ-CP Sửa đổi, bổ sung một số điều của các Nghị định của Chính phủ trong lĩnh vực quản lý nợ công (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187842)</t>
+          <t>• 84/2026/NĐ-CP — sửa đổi, bổ sung — hiệu lực 25/03/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187842</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr"/>
@@ -922,7 +933,28 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 100/2018/NĐ-CP Sửa đổi, bổ sung, bãi bỏ một số quy định về điều kiện đầu tư kinh doanh thuộc các lĩnh vực quản lý nhà n (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=130011) | bãi bỏ: Nghị định số 96/2024/NĐ-CP Quy định chi tiết một số điều của Luật Kinh doanh bất động sản (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=169708) | bãi bỏ: Nghị định số 207/2026/NĐ-CP Quy định chi tiết một số điều của Luật Xây dựng về quản lý chất lượng, thi công xây dựng và bảo trì công trình x (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=c4911dc0-6e5b-11f1-b871-73e465f01c71) | bãi bỏ: Nghị định số 35/2026/NĐ-CP Quy định chi tiết một số điều của Nghị quyết về phân loại đô thị (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186907) | hợp nhất: Văn bản hợp nhất số 15/VBHN-BXD Nghị định về quản lý đầu tư phát triển đô thị (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=162924) | hợp nhất: Văn bản hợp nhất số 03/VBHN-BXD Nghị định về quản lý đầu tư phát triển đô thị (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=160736) | hợp nhất: Văn bản hợp nhất số 07/VBHN-BXD NGhị định về quản lý đầu tư phát triển đô thị (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=131170) | hợp nhất: Văn bản hợp nhất số 07/VBHN-BXD NGhị định về quản lý đầu tư phát triển đô thị (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=131171) | hợp nhất: Văn bản hợp nhất số 04/VBHN-BXD Nghị định về quản lý đầu tư phát triển đô thị (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=171791) | sửa đổi, bổ sung: Nghị định số 31/2021/NĐ-CP Quy định chi tiết và hướng dẫn thi hành một số điều của Luật Đầu tư (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=147720) | sửa đổi, bổ sung: Nghị định số 35/2023/NĐ-CP sửa đổi, bổ sung một số điều của các Nghị định thuộc lĩnh vực quản lý nhà nước của Bộ Xây dựng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=160908)</t>
+          <t>• 100/2018/NĐ-CP — bãi bỏ — hiệu lực 15/09/2018
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=130011
+• 31/2021/NĐ-CP — sửa đổi, bổ sung — hiệu lực 26/03/2021
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=147720
+• 35/2023/NĐ-CP — sửa đổi, bổ sung — hiệu lực 20/06/2023
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=160908
+• 96/2024/NĐ-CP — bãi bỏ — hiệu lực 01/08/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=169708
+• 35/2026/NĐ-CP — bãi bỏ — hiệu lực 22/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186907
+• 207/2026/NĐ-CP — bãi bỏ — hiệu lực 01/07/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=c4911dc0-6e5b-11f1-b871-73e465f01c71
+• 03/VBHN-BXD — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=160736
+• 04/VBHN-BXD — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=171791
+• 07/VBHN-BXD — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=131170
+• 07/VBHN-BXD — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=131171
+• 15/VBHN-BXD — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=162924</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr"/>
@@ -964,7 +996,10 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 03/VBHN-BTC Hướng dẫn về phí và lệ phí thuộc thẩm quyền quyết định của Hội đồng nhân dân tỉnh, thành phố trực thuộc trun (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=156563) | sửa đổi, bổ sung: Thông tư số 106/2021/TT-BTC Sửa đổi, bổ sung một số điều của Thông tư số 85/2019/TT-BTC ngày 29 tháng 11 năm 2019 của Bộ trưởng Bộ Tài chính (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152278)</t>
+          <t>• 106/2021/TT-BTC — sửa đổi, bổ sung — hiệu lực 10/01/2022
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152278
+• 03/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=156563</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr"/>
@@ -1006,7 +1041,28 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 41/2026/TT-BCT Quy định Danh mục phế liệu và Danh mục hàng hóa đã qua sử dụng tạm ngừng kinh doanh tạm nhập, tái xuất, chuyển kh (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=bccbb3d0-873c-11f1-82a9-63ca2e29bb67) | hợp nhất: Văn bản hợp nhất số 29/VBHN-BCT Thông tư Quy định chi tiết một số điều của Luật Quản lý ngoại thương và Nghị định số 69/2018/NĐ-CP ngày 15 t (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179760) | hợp nhất: Văn bản hợp nhất số 06/VBHN-BCT Quy định chi tiết một số điều của Luật Quản lý ngoại thương và Nghị định số 69/2018/NĐ-CP ngày 15 tháng 5 nă (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=141174) | hợp nhất: Văn bản hợp nhất số 11/VBHN-BCT Thông tư bổ sung Danh mục chi tiết theo mã số HS của hàng hóa xuất khẩu, nhập khẩu quy định tại một số Thông (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=160168) | hợp nhất: Văn bản hợp nhất số 24/VBHN-BCT Thông tư quy định chi tiết một số điều của Luật Quản lý ngoại thương và Nghị định số 69/2018/NĐ-CP ngày 15 t (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=8ad6daf0-7f6f-11f1-9e1f-cba12064fd97) | hợp nhất: Văn bản hợp nhất số 47/VBHN-BCT Thông tư quy định chi tiết một số điều của Luật Quản lý ngoại thương và Nghị định số 69/2018/NĐ-CP ngày 15 t (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=14214f70-6891-11f1-801e-4db6a607ef12) | hợp nhất: Văn bản hợp nhất số 70/2026/VBHN-TT-BCT Thông tư quy định chi tiết một số điều của Luật Quản lý ngoại thương và Nghị định số 69/2018/NĐ-CP n (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=d7e65af0-926b-11f1-a5a9-cb03c709c8ec) | sửa đổi, bổ sung: Thông tư 26/2026/TT-BCT Sửa đổi, bổ sung một số quy định về phân cấp, cắt giảm, đơn giản hóa thủ tục hành chính trong các lĩnh vực thuộc phạ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=c38d4c80-5819-11f1-8cfa-090ca3b5a55f) | sửa đổi, bổ sung: Thông tư số 38/2025/TT-BCT sửa đổi, bổ sung một số quy định về phân cấp thực hiện thủ tục hành chính trong các lĩnh vực thuộc phạm vi quản l (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178549) | sửa đổi, bổ sung: Thông tư số 08/2023/TT-BCT sửa đổi, bổ sung một số điều quy định Danh mục chi tiết theo mã số HS của hàng hóa xuất khẩu, nhập khẩu ban hành  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=160072) | sửa đổi, bổ sung: Thông tư số 42/2019/TT-BCT Sửa đổi, bổ sung một số quy định về chế độ báo cáo định kỳ tại các Thông tư do Bộ trưởng Bộ Công Thương ban hành  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=139672)</t>
+          <t>• 42/2019/TT-BCT — sửa đổi, bổ sung — hiệu lực 05/02/2020
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=139672
+• 08/2023/TT-BCT — sửa đổi, bổ sung — hiệu lực 16/05/2023
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=160072
+• 38/2025/TT-BCT — sửa đổi, bổ sung — hiệu lực 01/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178549
+• Thông tư 26/2026/TT-BCT Sửa đổi, bổ sung một số quy định về phân cấp, cắt giảm, đơn giản h — sửa đổi, bổ sung — hiệu lực 29/05/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=c38d4c80-5819-11f1-8cfa-090ca3b5a55f
+• 41/2026/TT-BCT — bãi bỏ — hiệu lực 05/09/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=bccbb3d0-873c-11f1-82a9-63ca2e29bb67
+• 06/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=141174
+• 11/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=160168
+• 24/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=8ad6daf0-7f6f-11f1-9e1f-cba12064fd97
+• 29/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179760
+• 47/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=14214f70-6891-11f1-801e-4db6a607ef12
+• 70/2026/VBHN-TT-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=d7e65af0-926b-11f1-a5a9-cb03c709c8ec</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr"/>
@@ -1048,7 +1104,14 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Nghị định số 55/2023/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 75/2021/NĐ-CP ngày 24/7/2021 quy định mức hưởng trợ cấp, phụ cấp và (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=169616) | sửa đổi, bổ sung: Nghị định số 77/2024/NĐ-C Sửa đổi, bổ sung một số điều của Nghị định số 75/2021/NĐ-CP ngày 24 tháng 7 năm 2021 của Chính phủ quy định mức hư (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173646) | thay thế: Nghị định số 321/2026/NĐ-CP quy định mức hưởng trợ cấp, phụ cấp và các chế độ ưu đãi người có công với cách mạng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=5bfb4a00-9c83-11f1-9722-67b318d484b4) | thay thế: Nghị quyết số 26/2026/NQ-CP Về cơ chế, chính sách đặc thù nhằm tháo gỡ khó khăn trong tổ chức lấy mẫu, giám định và xác định danh tính hài c (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=539a1450-7a13-11f1-bfab-2d6d51f414a0)</t>
+          <t>• 55/2023/NĐ-CP — sửa đổi, bổ sung — hiệu lực 05/09/2023
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=169616
+• 77/2024/NĐ-C — sửa đổi, bổ sung — hiệu lực 01/07/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173646
+• 26/2026/NQ-CP — thay thế — hiệu lực 06/05/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=539a1450-7a13-11f1-bfab-2d6d51f414a0
+• 321/2026/NĐ-CP — thay thế — hiệu lực 01/10/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=5bfb4a00-9c83-11f1-9722-67b318d484b4</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr"/>
@@ -1090,7 +1153,8 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>thay thế: Thông tư số 45/2009/TT-BCA(C11) Hướng dẫn thi hành một số điều của Nghị định số 52/2008/NĐ-CP ngày 22 tháng 4 năm 2008 về quản lý kinh doanh (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=11741)</t>
+          <t>• 45/2009/TT-BCA(C11) — thay thế — hiệu lực 28/08/2009
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=11741</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr"/>
@@ -1132,7 +1196,22 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 92/2023/NĐ-CP Bãi bỏ một số văn bản quy phạm pháp luật của Chính phủ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=164308) | hợp nhất: Văn bản hợp nhất số 951/VBHN-BTP Quy định chi tiết thi hành một số điều của Luật nuôi con nuôi (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=134587) | hợp nhất: Văn bản hợp nhất số 275/VBHN-BTP Quy định chi tiết thi hành một số điều của Luật Nuôi con nuôi (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174653) | sửa đổi, bổ sung: Nghị định số 24/2019/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 19/2011/NĐ-CP ngày 21 tháng 3 năm 2011 của Chính phủ quy định chi t (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=134536) | sửa đổi, bổ sung: Nghị định số 18/2026/NĐ-CP Sửa đổi, bổ sung một số nghị định để cắt giảm, đơn giản hóa thủ tục hành chính, điều kiện kinh doanh thuộc phạm v (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187582) | sửa đổi, bổ sung: Nghị định số 06/2025/NĐ-CP Sửa đổi, bổ sung một số điều của các Nghị định về nuôi con nuôi (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174313) | sửa đổi, bổ sung: Nghị định số 114/2016/NĐ-CP Quy định lệ phí đăng ký nuôi con nuôi, lệ phí cấp giấy phép hoạt động của tổ chức con nuôi nước ngoài (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=112160) | sửa đổi, bổ sung: Nghị định số 104/2022/NĐ-CP Sửa đổi, bổ sung một số điều của các nghị định liên quan đến việc nộp, xuất trình sổ hộ khẩu, sổ tạm trú giấy kh (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=167220)</t>
+          <t>• 114/2016/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/01/2017
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=112160
+• 24/2019/NĐ-CP — sửa đổi, bổ sung — hiệu lực 25/04/2019
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=134536
+• 104/2022/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/01/2023
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=167220
+• 92/2023/NĐ-CP — bãi bỏ — hiệu lực 19/12/2023
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=164308
+• 06/2025/NĐ-CP — sửa đổi, bổ sung — hiệu lực 08/01/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174313
+• 18/2026/NĐ-CP — sửa đổi, bổ sung — hiệu lực 15/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187582
+• 275/VBHN-BTP — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174653
+• 951/VBHN-BTP — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=134587</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr"/>
@@ -1174,7 +1253,8 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Thông tư số 15/2018/TT-BTC Quy định về chi phí phát hành, hoán đểi, mua lại, thanh toán gốc, lãi trái phiếu Chính phủ, trái phiếu đuọc Chính (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=128189)</t>
+          <t>• 15/2018/TT-BTC — sửa đổi, bổ sung — hiệu lực 01/04/2018
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=128189</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr"/>
@@ -1216,7 +1296,14 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 156/2025/TT-BTC Sửa đổi, bổ sung một số điều của Thông tư số 199/2016/TT-BTC ngày 08 tháng 11 năm 2016 của Bộ trưởng Bộ Tài chín (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186182) | bãi bỏ: Thông tư 30/2026/TT-BTC Quy định mức thu, chế độ thu, nộp phí thẩm định cấp giấy phép hoạt động điện lực (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=f9b4a860-5a3c-11f1-9b9f-173bd8f4ab4f) | bãi bỏ: Thông tư số 11/2026/TT-BTС Quy định mức thu, chế độ thu, nộp phí thuộc lĩnh vực đường sắt (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186990) | sửa đổi, bổ sung: Thông tư 11/2026/TT-BTC Quy định mức thu, chế độ thu, nộp phí thuộc lĩnh vực đường sắt (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=bf3acd10-599f-11f1-bcbf-37bff26920b0) | sửa đổi, bổ sung: Thông tư số 11/2026/TT-BTС Quy định mức thu, chế độ thu, nộp phí thuộc lĩnh vực đường sắt (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186990)</t>
+          <t>• 156/2025/TT-BTC — bãi bỏ — hiệu lực 01/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186182
+• 11/2026/TT-BTС — bãi bỏ, sửa đổi, bổ sung — hiệu lực 27/03/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186990
+• Thông tư 11/2026/TT-BTC Quy định mức thu, chế độ thu, nộp phí thuộc lĩnh vực đường sắt — sửa đổi, bổ sung — hiệu lực 27/03/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=bf3acd10-599f-11f1-bcbf-37bff26920b0
+• Thông tư 30/2026/TT-BTC Quy định mức thu, chế độ thu, nộp phí thẩm định cấp giấy phép hoạt — bãi bỏ — hiệu lực 11/05/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=f9b4a860-5a3c-11f1-9b9f-173bd8f4ab4f</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr"/>
@@ -1258,7 +1345,8 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Thông tư số 56/2023/TT-BGTVT Sửa đổi, bổ sung một số Điều của Thông tư số 23/2017/TT-BGTVT ngày 28 tháng 07 năm 2017 của Bộ trưởng Bộ Giao t (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=165446)</t>
+          <t>• 56/2023/TT-BGTVT — sửa đổi, bổ sung — hiệu lực 01/04/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=165446</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr"/>
@@ -1300,7 +1388,32 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 07/VBHN-NHNN Quy định về giao nhận, bảo quản, vận chuyển tiền mặt, tài sản quý, giấy tờ có giá (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178572) | hợp nhất: Văn bản hợp nhất số 24/VBHN-NHNN Thông tư hướng dẫn việc tổ chức thực hiện hoạt động quản lý dự trữ ngoại hối nhà nước (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=164720) | hợp nhất: Văn bản hợp nhất số 32/VBHN-NHNN Hướng dẫn việc tổ chức thực hiện hoạt động quản lý dự trữ ngoại hối nhà nước (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=170802) | hợp nhất: Văn bản hợp nhất số 07/VBHN-NHNN Quy định về giao nhận, bảo quản, vận chuyển tiền mặt, tài sản quý, giấy tờ có giá (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179742) | hợp nhất: Văn bản hợp nhất số 08/VBHN-NHNN Quy định về giao nhận, bảo quản, vận chuyển tiền mặt, tài sản quý, giấy tờ có giá (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=127031) | hợp nhất: Văn bản hợp nhất số 26/VBHN-NHNN Quy định về giao nhận, bảo quản, vận chuyển tiền mặt, tài sản quý, giấy tờ có giá (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=138098) | hợp nhất: Văn bản hợp nhất số 14/VBHN-NHNN Quy định về giao nhận, bảo quản, vận chuyển tiền mặt, tài sản quý, giấy tờ có giá (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=151816) | sửa đổi, bổ sung: Thông tư số 12/2023/TT-NHNN Sửa đổi, bổ sung một số điều của các văn bản quy phạm pháp luật quy định về việc triển khai nhiệm vụ quản lý dự  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=162635) | sửa đổi, bổ sung: Thông tư số 19/2021/TT-NHNN Sửa đổi, bổ sung một số điều của Thông tư số 01/2014/TT-NHNN ngày 06/01/2014 của Thống đốc Ngân hàng Nhà nước Vi (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=150860) | sửa đổi, bổ sung: Thông tư số 43/2024/TT-NHNN sửa đổi, bổ sung một số điều của Thông tư số 01/2014/TT-NHNN ngày 10 tháng 12 năm 2014 của Thống đốc Ngân hàng N (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=169221) | sửa đổi, bổ sung: Thông tư số 14/2019/TT-NHNN Sửa đổi, bổ sung một số điều tại các Thông tư có quy định về chế độ báo cáo định kỳ của Ngân hàng Nhà nước (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=137583) | sửa đổi, bổ sung: Thông tư số 05/2025/TT-NHNN Sửa đổi, bổ sung một số điều của Thông tư số 01/2014/TT-NHNN ngày 06/01/2014 của Thống đốc Ngân hàng Nhà nước Vi (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178168) | sửa đổi, bổ sung: Thông tư số 12/2017/TT-NHNN Sửa đổi, bổ sung một số điều của Thông tư số 01/2014/TT-NHNN ngày 06/01/2014 của Thống đốc Ngân hàng Nhà nước Vi (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=124628)</t>
+          <t>• 12/2017/TT-NHNN — sửa đổi, bổ sung — hiệu lực 16/10/2017
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=124628
+• 14/2019/TT-NHNN — sửa đổi, bổ sung — hiệu lực 15/10/2019
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=137583
+• 19/2021/TT-NHNN — sửa đổi, bổ sung — hiệu lực 08/01/2022
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=150860
+• 12/2023/TT-NHNN — sửa đổi, bổ sung — hiệu lực 27/11/2023
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=162635
+• 43/2024/TT-NHNN — sửa đổi, bổ sung — hiệu lực 23/09/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=169221
+• 05/2025/TT-NHNN — sửa đổi, bổ sung — hiệu lực 19/05/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178168
+• 07/VBHN-NHNN — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178572
+• 07/VBHN-NHNN — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179742
+• 08/VBHN-NHNN — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=127031
+• 14/VBHN-NHNN — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=151816
+• 24/VBHN-NHNN — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=164720
+• 26/VBHN-NHNN — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=138098
+• 32/VBHN-NHNN — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=170802</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr"/>
@@ -1342,7 +1455,10 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 25/2018/TT-BYT bãi bỏ một số văn bản quy phạm pháp luật trong lĩnh vực y tế Bộ trưởng Bộ Y tế ban hành, liên tịch ban hành (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=137196) | bãi bỏ: Thông tư số 20/2023/TT-BYT Bãi bỏ một số văn bản quy phạm pháp luật do Bộ trưởng Bộ Y tế ban hành (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=166212)</t>
+          <t>• 25/2018/TT-BYT — bãi bỏ — hiệu lực 15/11/2018
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=137196
+• 20/2023/TT-BYT — bãi bỏ — hiệu lực 01/01/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=166212</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr"/>
@@ -1384,7 +1500,8 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 29/2018/TT-BCT Sửa đổi, bổ sung một số Thông tư quy định chế độ báo cáo định kỳ trong lĩnh vực Công Thương (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133197)</t>
+          <t>• 29/2018/TT-BCT — bãi bỏ — hiệu lực 12/11/2018
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133197</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr"/>
@@ -1426,7 +1543,16 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 87/2015/TT-BGTVT Ban hành Quy chuẩn kỹ thuật quốc gia về chất lượng an toàn kỹ thuật và bảo vệ môi trường đối với xe ô tô (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111822) | bãi bỏ: Thông tư số 90/2015/TT-BGTVT Ban hành Quy chuẩn kỹ thuật quốc gia về chất lượng an toàn kỹ thuật và bảo vệ môi trường đối với ô tô khách thà (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111612) | bãi bỏ: Thông tư số 45/2023/TT-BGTVT Ban hành Quy chuẩn kỹ thuật quốc gia về chất lượng an toàn kỹ thuật và bảo vệ môi trường đối với xe máy chuyên  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=164732) | bãi bỏ: Thông tư số 88/2015/TT-BGTVT Ban hành Quy chuẩn kỹ thuật quốc gia về chất lượng an toàn kỹ thuật đối với rơ moóc và sơ mi rơ moóc (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=98556) | bãi bỏ: Thông tư số 67/2015/TT-BGTVT Ban hành Quy chuẩn kỹ thuật quốc gia về chất lượng an toàn kỹ thuật và bảo vệ môi trường đối với xe mô tô, xe g (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111835)</t>
+          <t>• 67/2015/TT-BGTVT — bãi bỏ — hiệu lực 01/07/2016
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111835
+• 87/2015/TT-BGTVT — bãi bỏ — hiệu lực 01/07/2016
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111822
+• 88/2015/TT-BGTVT — bãi bỏ — hiệu lực 01/07/2016
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=98556
+• 90/2015/TT-BGTVT — bãi bỏ — hiệu lực 01/07/2016
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111612
+• 45/2023/TT-BGTVT — bãi bỏ — hiệu lực 01/07/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=164732</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr"/>
@@ -1468,7 +1594,10 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 42/2019/TT-BCT Sửa đổi, bổ sung một số quy định về chế độ báo cáo định kỳ tại các Thông tư do Bộ trưởng Bộ Công Thương ban hành  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=139672) | hợp nhất: Văn bản hợp nhất số 37/VBHN-BCT Ban hành Quy chuẩn kỹ thuật quốc gia đối với sản phẩm khăn giấy và giấy vệ sinh (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=141720)</t>
+          <t>• 42/2019/TT-BCT — bãi bỏ — hiệu lực 05/02/2020
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=139672
+• 37/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=141720</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr"/>
@@ -1510,7 +1639,14 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 23/2024/TT-BTTTT bãi bỏ một số văn bản quy phạm pháp luật do Bộ trưởng Bộ Thông tin và Truyền thông ban hành hoặc liên tịch ban  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174567) | bãi bỏ: Thông tư số 23/2024/TT-BKHCN Bãi bỏ một số văn bản quy phạm pháp luật do Bộ trưởng Bộ Thông tin và Truyền thông ban hành hoặc liên tịch ban  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=184410) | sửa đổi, bổ sung: Thông tư số 10/2020/TT-BTTTT Sửa đổi, bổ sung một số nội dung của Thông tư số 30/2011/TT-BTTTT ngày 31 tháng 10 năm 2011 của Bộ trưởng Bộ Th (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=146204) | sửa đổi, bổ sung: Thông tư số 15/2018/TT-BTTTT Sửa đổi, bổ sung một số nội dung của Thông tư số 30/2011/TT-BTTTT ngày 31 tháng 10 năm 2011 của Bộ trưởng Bộ Th (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133255)</t>
+          <t>• 15/2018/TT-BTTTT — sửa đổi, bổ sung — hiệu lực 01/01/2019
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133255
+• 10/2020/TT-BTTTT — sửa đổi, bổ sung — hiệu lực 01/07/2020
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=146204
+• 23/2024/TT-BKHCN — bãi bỏ — hiệu lực 31/12/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=184410
+• 23/2024/TT-BTTTT — bãi bỏ — hiệu lực 31/12/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174567</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr"/>
@@ -1552,7 +1688,12 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 22/2016/TT-BXD Bãi bỏ toàn bộ hoặc một phần văn bản quy phạm pháp luật có quy định về điều kiện đầu tư kinh doanh do Bộ Xây dựng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=112527) | sửa đổi, bổ sung: Thông tư số 06/2011/TT-BXD Sửa đổi Quy định về thủ tục hành chính trong lĩnh vực xây dựng; kiến trúc, quy hoạch xây dựng thực thi Nghị quyết (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26668) | thay thế: Thông tư số 17/2016/TT-BXD Hướng dẫn về năng lực của tổ chức, cá nhân tham gia hoạt động xây dựng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111687)</t>
+          <t>• 06/2011/TT-BXD — sửa đổi, bổ sung — hiệu lực 05/08/2011
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26668
+• 22/2016/TT-BXD — bãi bỏ — hiệu lực 01/07/2016
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=112527
+• 17/2016/TT-BXD — thay thế — hiệu lực 01/09/2016
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111687</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr"/>
@@ -1594,7 +1735,10 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 01/VBHN-BTTTT Quy định chi tiết và hướng dẫn thi hành một số điều của Luật Xuất bản và Nghị định số 195/2013/NĐ-CP ngày  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=166347) | sửa đổi, bổ sung: Thông tư số 23/2023/TT-BTTTT Sửa đổi, bổ sung một số điều của Thông tư số 01/2020/TT-BTTTT ngày 07 tháng 02 năm 2020 của Bộ trưởng Bộ Thông  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=166015)</t>
+          <t>• 23/2023/TT-BTTTT — sửa đổi, bổ sung — hiệu lực 07/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=166015
+• 01/VBHN-BTTTT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=166347</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr"/>
@@ -1636,7 +1780,12 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư 20/2026/TT-BTC Quy định chi tiết một số điều của Luật Thuế thu nhập doanh nghiệp và Nghị định số 320/2025/NĐ-CP ngày 15 tháng 12 nă (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=6fb7dd80-59a6-11f1-a013-532655e6581a) | bãi bỏ: Nghị định số 18/2021/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 134/2016/NĐ-CP ngày 01 tháng 9 năm 2016 của Chính phủ quy định chi  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=151157) | sửa đổi, bổ sung: Thông tư số 81/2018/TT-BTC Sửa đổi, bổ sung Thông tư số 83/2016/TT-BTC ngày 17/6/2016 của Bộ Tài chính hướng dẫn thực hiện ưu đãi đầu tư the (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135988)</t>
+          <t>• 81/2018/TT-BTC — sửa đổi, bổ sung — hiệu lực 12/10/2018
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135988
+• 18/2021/NĐ-CP — bãi bỏ — hiệu lực 25/04/2021
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=151157
+• Thông tư 20/2026/TT-BTC Quy định chi tiết một số điều của Luật Thuế thu nhập doanh nghiệp  — bãi bỏ — hiệu lực 10/03/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=6fb7dd80-59a6-11f1-a013-532655e6581a</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr"/>
@@ -1678,7 +1827,18 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 40/2026/NĐ-CP Quy định chi tiết một số điều của Luật Thủy lợi (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=a0526ee0-791f-11f1-a7d3-6f8ab17b527d) | bãi bỏ: Nghị định số 32/2026/NĐ-CP Sửa đổi, bổ sung một số điều của các Nghị định trong lĩnh vực chăn nuôi và thú y (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=aaff53a0-767f-11f1-a26c-15d47590a02f) | bãi bỏ: Nghị định số 39/2026/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 27/2019/NĐ-CP ngày 13 tháng 3 năm 2019 của Chính phủ quy định chi t (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187831) | bãi bỏ: Nghị định số 23/2026/NĐ-CP Sửa đổi, bổ sung một số điều của các nghị định trong lĩnh vực tài nguyên nước (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186456) | bãi bỏ: Nghị định số 48/2026/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 08/2022/NĐ-CP ngày 10 tháng 01 năm 2022 của Chính phủ quy định chi  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187432) | thay thế: Nghị định số 43/2026/NĐ-CP Sửa đổi, bổ sung một số điều của các nghị định trong lĩnh vực bảo tồn thiên nhiên và đa dạng sinh học (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186739)</t>
+          <t>• 23/2026/NĐ-CP — bãi bỏ — hiệu lực 17/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186456
+• 32/2026/NĐ-CP — bãi bỏ — hiệu lực 21/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=aaff53a0-767f-11f1-a26c-15d47590a02f
+• 39/2026/NĐ-CP — bãi bỏ — hiệu lực 25/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187831
+• 40/2026/NĐ-CP — bãi bỏ — hiệu lực 25/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=a0526ee0-791f-11f1-a7d3-6f8ab17b527d
+• 43/2026/NĐ-CP — thay thế — hiệu lực 26/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186739
+• 48/2026/NĐ-CP — bãi bỏ — hiệu lực 29/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187432</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr"/>
@@ -1720,7 +1880,14 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 198/2025/NĐ-CP Quy định chi tiết một số điều và biện pháp thi hành Luật Phòng không nhân dân (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179783) | bãi bỏ: Nghị định số 222/2026/NĐ-CP về hoạt động bay (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=b6ab9020-8bbe-11f1-b2d0-6b22a52408be) | hợp nhất: Văn bản hợp nhất số 20/VBHN-BQP Quy định về quản lý độ cao chướng ngại vật hàng không và các trận địa quản lý, bảo vệ vùng trời tại Việt Nam (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179790) | sửa đổi, bổ sung: Nghị định số 101/2025/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 32/2016/NĐ-CP ngày 06 tháng 5 năm 2016 của Chính phủ quy định về q (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=177726)</t>
+          <t>• 101/2025/NĐ-CP — sửa đổi, bổ sung — hiệu lực 23/06/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=177726
+• 198/2025/NĐ-CP — bãi bỏ — hiệu lực 22/08/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179783
+• 222/2026/NĐ-CP — bãi bỏ — hiệu lực 01/07/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=b6ab9020-8bbe-11f1-b2d0-6b22a52408be
+• 20/VBHN-BQP — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179790</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr"/>
@@ -1762,7 +1929,18 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 17/VBHN-BNNPTNT Quy định chi tiết thi hành một số điều của Luật Lâm nghiệp (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=166617) | hợp nhất: Văn bản hợp nhất số 24/VBHN-BNNPTNT Quy định chi tiết thi hành một số điều của Luật Lâm nghiệp (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=172573) | sửa đổi, bổ sung: Nghị định số 183/2025/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 156/2018/NĐ-CP ngày 16 tháng 11 năm 2018 của Chính phủ quy định ch (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179099) | sửa đổi, bổ sung: Nghị định số 91/2024/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 156/2018/NĐ-CP ngày 16 tháng 11 năm 2018 của Chính phủ quy định chi (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=168695) | sửa đổi, bổ sung: Nghị định số 227/2025/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 156/2018/NĐ-CP ngày 16 tháng 11 năm 2018 của Chính phủ quy định ch (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186289) | thay thế: Nghị định số 58/2024/NĐ-CP Một số chính sách đầu tư trong lâm nghiệp (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=167508) | thay thế: Nghị định số 227/2025/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 156/2018/NĐ-CP ngày 16 tháng 11 năm 2018 của Chính phủ quy định ch (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186289)</t>
+          <t>• 58/2024/NĐ-CP — thay thế — hiệu lực 15/07/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=167508
+• 91/2024/NĐ-CP — sửa đổi, bổ sung — hiệu lực 18/07/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=168695
+• 183/2025/NĐ-CP — sửa đổi, bổ sung — hiệu lực 15/08/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179099
+• 227/2025/NĐ-CP — sửa đổi, bổ sung, thay thế — hiệu lực 16/08/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186289
+• 17/VBHN-BNNPTNT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=166617
+• 24/VBHN-BNNPTNT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=172573</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr"/>
@@ -1804,7 +1982,22 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 92/2023/NĐ-CP Bãi bỏ một số văn bản quy phạm pháp luật của Chính phủ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=164308) | hợp nhất: Văn bản hợp nhất số 951/VBHN-BTP Quy định chi tiết thi hành một số điều của Luật nuôi con nuôi (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=134587) | hợp nhất: Văn bản hợp nhất số 275/VBHN-BTP Quy định chi tiết thi hành một số điều của Luật Nuôi con nuôi (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174653) | sửa đổi, bổ sung: Nghị định số 24/2019/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 19/2011/NĐ-CP ngày 21 tháng 3 năm 2011 của Chính phủ quy định chi t (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=134536) | sửa đổi, bổ sung: Nghị định số 18/2026/NĐ-CP Sửa đổi, bổ sung một số nghị định để cắt giảm, đơn giản hóa thủ tục hành chính, điều kiện kinh doanh thuộc phạm v (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187582) | sửa đổi, bổ sung: Nghị định số 06/2025/NĐ-CP Sửa đổi, bổ sung một số điều của các Nghị định về nuôi con nuôi (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174313) | sửa đổi, bổ sung: Nghị định số 114/2016/NĐ-CP Quy định lệ phí đăng ký nuôi con nuôi, lệ phí cấp giấy phép hoạt động của tổ chức con nuôi nước ngoài (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=112160) | sửa đổi, bổ sung: Nghị định số 104/2022/NĐ-CP Sửa đổi, bổ sung một số điều của các nghị định liên quan đến việc nộp, xuất trình sổ hộ khẩu, sổ tạm trú giấy kh (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=167220)</t>
+          <t>• 114/2016/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/01/2017
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=112160
+• 24/2019/NĐ-CP — sửa đổi, bổ sung — hiệu lực 25/04/2019
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=134536
+• 104/2022/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/01/2023
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=167220
+• 92/2023/NĐ-CP — bãi bỏ — hiệu lực 19/12/2023
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=164308
+• 06/2025/NĐ-CP — sửa đổi, bổ sung — hiệu lực 08/01/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174313
+• 18/2026/NĐ-CP — sửa đổi, bổ sung — hiệu lực 15/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187582
+• 275/VBHN-BTP — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174653
+• 951/VBHN-BTP — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=134587</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr"/>
@@ -1846,7 +2039,10 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 07/2021/TT-BVHTTDL quy định về tập huấn chuyên môn thể thao đối với người hướng dẫn tập luyện thể thao. (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=149703) | bãi bỏ: Thông tư số 21/2025/TT-BVHTTDL sửa đổi, bổ sung một số điều của các Thông tư có quy định thủ tục hành chính liên quan đến hoạt động sản xuất (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186002)</t>
+          <t>• 07/2021/TT-BVHTTDL — bãi bỏ — hiệu lực 01/12/2021
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=149703
+• 21/2025/TT-BVHTTDL — bãi bỏ — hiệu lực 26/12/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186002</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr"/>
@@ -1888,7 +2084,10 @@
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Nghị định số 42/2024/NĐ-CP Về hoạt động lấn biển (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=167334) | sửa đổi, bổ sung: Nghị định số 104/2022/NĐ-CP Sửa đổi, bổ sung một số điều của các nghị định liên quan đến việc nộp, xuất trình sổ hộ khẩu, sổ tạm trú giấy kh (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=167220)</t>
+          <t>• 104/2022/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/01/2023
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=167220
+• 42/2024/NĐ-CP — sửa đổi, bổ sung — hiệu lực 16/04/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=167334</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr"/>
@@ -1930,7 +2129,16 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 40/2024/TT-BGTVT Quy định về công tác phòng, chống, khắc phục hậu quả thiên tai trong lĩnh vực đường bộ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174157) | sửa đổi, bổ sung: Thông tư số 25/2024/TT-BGTVT Sửa đổi, bổ sung một số điều của Thông tư số 50/2015/TT-BGTVT ngày 23 tháng 9 năm 2015 của Bộ trưởng Bộ Giao th (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=168214) | sửa đổi, bổ sung: Thông tư số 43/2021/TT-BGTVT Sửa đổi, bổ sung một số điều của Thông tư số 03/2019/TT-BGTVT ngày 11 tháng 01 năm 2019 của Bộ trưởng Bộ Giao t (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152588) | sửa đổi, bổ sung: Thông tư số 36/2020/TT-BGTVT Sửa đổi, bổ sung một số điều của các Thông tư quy định về chế độ báo cáo định kỳ trong lĩnh vực đường bộ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=145902) | sửa đổi, bổ sung: Thông tư số 22/2023/TT-BGTVT Sửa đổi, bổ sung một số điều của Thông tư số 03/2019/TT-BGTVT ngày 11 tháng 01 năm 2019 của Bộ trưởng Bộ Giao t (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=163042)</t>
+          <t>• 36/2020/TT-BGTVT — sửa đổi, bổ sung — hiệu lực 15/02/2021
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=145902
+• 43/2021/TT-BGTVT — sửa đổi, bổ sung — hiệu lực 01/03/2022
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152588
+• 22/2023/TT-BGTVT — sửa đổi, bổ sung — hiệu lực 15/08/2023
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=163042
+• 25/2024/TT-BGTVT — sửa đổi, bổ sung — hiệu lực 01/08/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=168214
+• 40/2024/TT-BGTVT — bãi bỏ — hiệu lực 01/01/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174157</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr"/>
@@ -1972,7 +2180,14 @@
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 14/2021/TT-BGTVT Bãi bỏ Điều 22 Thông tư số 31/2018/TT-BGTVT ngày 15 tháng 5 năm 2018 của Bộ trưởng Bộ Giao thông vận tải quy đị (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=167004) | bãi bỏ: Thông tư số 34/2025/TT-BXD Quy định về quản lý, khai thác kết cấu hạ tầng đường sắt (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=185678) | bãi bỏ: Thông tư số 01/2024/TT-BGTVT Quy định về việc kiểm tra chất lượng an toàn kỹ thuật và bảo vệ môi trường phương tiện giao thông đường sắt (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=166516) | bãi bỏ: Thông tư số 01/2022/TT-BGTVT Sửa đổi, bổ sung một số điều Thông tư số 29/2018/TT-BGTVT ngày 14 tháng 5 năm 2018 của Bộ trưởng Bộ Giao thông  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152592)</t>
+          <t>• 14/2021/TT-BGTVT — bãi bỏ — hiệu lực 01/08/2021
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=167004
+• 01/2022/TT-BGTVT — bãi bỏ — hiệu lực 01/03/2022
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152592
+• 01/2024/TT-BGTVT — bãi bỏ — hiệu lực 15/03/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=166516
+• 34/2025/TT-BXD — bãi bỏ — hiệu lực 01/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=185678</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr"/>
@@ -2014,7 +2229,14 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 37/2016/TT-BCT Sửa đổi, bổ sung một số điều của Thông tư số 50/2014/TT-BCT ngày 15 tháng 12 năm 2014 của Bộ trưởng Bộ Công Thươn (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135507) | bãi bỏ: Thông tư số 25/2024/TT-BCT Bãi bỏ toàn bộ một số văn bản quy phạm pháp luật do Bộ trưởng Bộ Công Thương ban hành, liên tịch ban hành (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=172166) | hợp nhất: Văn bản hợp nhất số 35/VBHN-BCT Quy định về quản lý nhiệm vụ khoa học và công nghệ của Bộ Công Thương (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=141722) | sửa đổi, bổ sung: Thông tư số 42/2019/TT-BCT Sửa đổi, bổ sung một số quy định về chế độ báo cáo định kỳ tại các Thông tư do Bộ trưởng Bộ Công Thương ban hành  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=139672)</t>
+          <t>• 37/2016/TT-BCT — bãi bỏ — hiệu lực 10/02/2017
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135507
+• 42/2019/TT-BCT — sửa đổi, bổ sung — hiệu lực 05/02/2020
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=139672
+• 25/2024/TT-BCT — bãi bỏ — hiệu lực 31/12/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=172166
+• 35/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=141722</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr"/>
@@ -2056,7 +2278,8 @@
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>thay thế: Quyết định số 12/2005/QĐ-BGTVT Ban hành Điều lệ đường ngang (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=16270)</t>
+          <t>• 12/2005/QĐ-BGTVT — thay thế — hiệu lực 12/02/2005
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=16270</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr"/>
@@ -2098,7 +2321,18 @@
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 01/2020/TT-BNNPTNT Quy định về chế độ báo cáo định kỳ thuộc phạm vi quản lý nhà nước của Bộ Nông nghiệp và Phát triển nông thôn (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=142035) | bãi bỏ: Thông tư số 06/2022/TT-BNNPTNT Sửa đổi, bổ sung một số điều của các Thông tư quy định về kiểm dịch động vật, sản phẩm động vật thủy sản (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=155158) | sửa đổi, bổ sung: Thông tư số 05/2025/TT-BNNMT Sửa đổi, bổ sung một số Thông tư trong lĩnh vực khai thác thuỷ sản (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178681) | sửa đổi, bổ sung: Thông tư số 01/2022/TT-BNNPTNT Sửa đổi, bổ sung một số Thông tư trong lĩnh vực thủy sản (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152678) | sửa đổi, bổ sung: Thông tư số 13/2020/TT-BNNPTNT Sửa đổi, bổ sung một số điều của Thông tư số 21/2018/TT-BNNPTNT ngày 15/11/2018 quy định ghi, nộp báo cáo, nh (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=144999) | thay thế: Thông tư số 81/2025/TT-BNNMT Quy định ghi, nộp báo cáo, nhật ký khai thác thủy sản; kiểm tra tàu cá và giám sát sản lượng thủy sản tại cảng  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186332)</t>
+          <t>• 01/2020/TT-BNNPTNT — bãi bỏ — hiệu lực 05/03/2020
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=142035
+• 13/2020/TT-BNNPTNT — sửa đổi, bổ sung — hiệu lực 25/12/2020
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=144999
+• 01/2022/TT-BNNPTNT — sửa đổi, bổ sung — hiệu lực 04/03/2022
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152678
+• 06/2022/TT-BNNPTNT — bãi bỏ — hiệu lực 11/09/2022
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=155158
+• 05/2025/TT-BNNMT — sửa đổi, bổ sung — hiệu lực 18/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178681
+• 81/2025/TT-BNNMT — thay thế — hiệu lực 01/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186332</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr"/>
@@ -2140,7 +2374,16 @@
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 63/2024/TT-NHNN Quy định về hồ sơ, thủ tục thu hồi Giấy phép và thanh lý tài sản của tổ chức tín dụng, chi nhánh ngân hàng nước  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174391) | hợp nhất: Văn bản hợp nhất số 29/VBHN-NHNN Quy định về trình tự, thủ tục thu hồi Giấy phép và thanh lý tài sản của tổ chức tín dụng, chi nhánh ngân hà (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=138117) | hợp nhất: Văn bản hợp nhất số 10/VBHN-NHNN Quy định về trình tự, thủ tục thu hồi Giấy phép và thanh lý tài sản của tổ chức tín dụng, chi nhánh ngân hà (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=145670) | sửa đổi, bổ sung: Thông tư số 11/2020/TT-NHNN Sửa đổi, bổ sung một số điều của Thông tư số 24/2017/TT-NHNN ngày 29 tháng 12 năm 2017 của Thống đốc Ngân hàng N (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=144726) | sửa đổi, bổ sung: Thông tư số 14/2019/TT-NHNN Sửa đổi, bổ sung một số điều tại các Thông tư có quy định về chế độ báo cáo định kỳ của Ngân hàng Nhà nước (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=137583) | thay thế: Thông tư số 63/2024/TT-NHNN Quy định về hồ sơ, thủ tục thu hồi Giấy phép và thanh lý tài sản của tổ chức tín dụng, chi nhánh ngân hàng nước  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174391)</t>
+          <t>• 14/2019/TT-NHNN — sửa đổi, bổ sung — hiệu lực 15/10/2019
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=137583
+• 11/2020/TT-NHNN — sửa đổi, bổ sung — hiệu lực 17/12/2020
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=144726
+• 63/2024/TT-NHNN — bãi bỏ, thay thế — hiệu lực 17/02/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174391
+• 10/VBHN-NHNN — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=145670
+• 29/VBHN-NHNN — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=138117</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr"/>
@@ -2182,7 +2425,10 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 4750/VBHN-BTP Quy định chế độ áp dụng biện pháp xử lý hành chính giáo dục tại xã, phường, đặc khu (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=180151) | sửa đổi, bổ sung: Nghị định số 190/2025/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 118/2021/NĐ-CP ngày 23 tháng 12 năm 2021 của Chính phủ quy định ch (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179389)</t>
+          <t>• 190/2025/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179389
+• 4750/VBHN-BTP — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=180151</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr"/>
@@ -2224,7 +2470,12 @@
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Nghị định số 18/2026/NĐ-CP Sửa đổi, bổ sung một số nghị định để cắt giảm, đơn giản hóa thủ tục hành chính, điều kiện kinh doanh thuộc phạm v (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187582) | sửa đổi, bổ sung: Nghị định số 112/2025/NĐ-CP Sửa đổi, bổ sung một số điều của các Nghị định thuộc lĩnh vực bổ trợ tư pháp (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178105) | thay thế: Nghị định số 112/2025/NĐ-CP Sửa đổi, bổ sung một số điều của các Nghị định thuộc lĩnh vực bổ trợ tư pháp (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178105) | thay thế: Nghị định số 65/2026/NĐ-CP Quy định chi tiết một số điều và biện pháp thi hành Luật Phục hồi, phá sản về Quản tài viên và hành nghề quản lý, (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187585)</t>
+          <t>• 112/2025/NĐ-CP — sửa đổi, bổ sung, thay thế — hiệu lực 29/05/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178105
+• 18/2026/NĐ-CP — sửa đổi, bổ sung — hiệu lực 15/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187582
+• 65/2026/NĐ-CP — thay thế — hiệu lực 01/03/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187585</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr"/>
@@ -2308,7 +2559,8 @@
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Luật Tổ chức Toà án nhân dân số số: 34/2024/QH15 (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=170570)</t>
+          <t>• Luật Tổ chức Toà án nhân dân số số: 34/2024/QH15 — bãi bỏ — hiệu lực 01/01/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=170570</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr"/>
@@ -2350,7 +2602,12 @@
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 61/2026/NĐ-CP Quy định về danh mục, việc quản lý, sử dụng phương tiện, thiết bị kỹ thuật nghiệp vụ và quy trình thu thập, sử dụ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187090) | sửa đổi, bổ sung: Nghị định số 301/2025/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 38/2024/NĐ-CP ngày 05 tháng 4 năm 2024 của Chính phủ quy định xử p (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186287) | thay thế: Nghị định số 246/2026/NĐ-CP Quy định xử phạt vi phạm hành chính trong lĩnh vực thủy sản (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=09419d10-79e6-11f1-b98d-21953d217c11)</t>
+          <t>• 301/2025/NĐ-CP — sửa đổi, bổ sung — hiệu lực 17/11/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186287
+• 61/2026/NĐ-CP — bãi bỏ — hiệu lực 01/04/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187090
+• 246/2026/NĐ-CP — thay thế — hiệu lực 18/08/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=09419d10-79e6-11f1-b98d-21953d217c11</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr"/>
@@ -2392,7 +2649,14 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 282/2025/NĐ-CP Quy định xử phạt vi phạm hành chính trong lĩnh vực an ninh, trật tự, an toàn xã hội; phòng, chống tệ nạn, xã hội (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=185254) | hợp nhất: Văn bản hợp nhất số 6545/VBHN-BTP Quy định xử phạt vi phạm hành chính trong lĩnh vực bổ trợ tư pháp; hành chính tư pháp; hôn nhân và gia đìn (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=171730) | sửa đổi, bổ sung: Nghị định số 117/2024/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 82/2020/NĐ-CP ngày 15 tháng 7 năm 2020 của Chính phủ quy định xử p (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=170131) | thay thế: Nghị định 109/2026/NĐ-CP Quy định xử phạt vi phạm hành chính trong lĩnh vực bổ trợ tư pháp; hành chính tư pháp; hôn nhân và gia đình; thi hà (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=0ae72df0-4247-11f1-9aef-8b444472143a)</t>
+          <t>• 117/2024/NĐ-CP — sửa đổi, bổ sung — hiệu lực 15/11/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=170131
+• 282/2025/NĐ-CP — bãi bỏ — hiệu lực 15/12/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=185254
+• Nghị định 109/2026/NĐ-CP Quy định xử phạt vi phạm hành chính trong lĩnh vực bổ trợ tư pháp — thay thế — hiệu lực 18/05/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=0ae72df0-4247-11f1-9aef-8b444472143a
+• 6545/VBHN-BTP — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=171730</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr"/>
@@ -2434,7 +2698,20 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 12/2024/TT-BTNMT Quy định chi tiết về đào tạo, bồi dưỡng, cập nhật kiến thức cho cá nhân hành nghề tư vấn định giá đất; khung ch (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173538) | bãi bỏ: Thông tư số 26/2024/TT-BTNMT Quy định kỹ thuật về đo đạc lập bản đồ địa chính (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174271) | bãi bỏ: Thông tư số 27/2018/TT-BTNMT Quy định về thống kê, kiểm kê đất đai và lập bản đồ hiện trạng sử dụng đất (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133433) | bãi bỏ: Thông tư số 02/2023/TT-BTNMT Sửa đổi, bổ sung một số điều của Thông tư số 23/2014/TT-BTNMT ngày 19 tháng 5 năm 2014 của Bộ trưởng Bộ Tài ngu (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=166137) | sửa đổi, bổ sung: Thông tư số 33/2017/TT-BTNMT Quy định chi tiết Nghị định số 01/2017/NĐ-CP ngày 06 tháng 01 năm 2017 của Chính phủ sửa đổi, bổ sung một số ng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=125567) | sửa đổi, bổ sung: Thông tư số 13/2019/TT-BTNMT Ban hành Quy định Định mức kinh tế - kỹ thuật thống kê, kiểm kê đất đai và lập bản đồ hiện trạng sử dụng đất (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=137027) | sửa đổi, bổ sung: Thông tư số 09/2021/TT-BTNMT Sửa đổi, bổ sung một số điều của các Thông tư quy định chi tiết và hướng dẫn thi hành Luật Đất đai (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=149005)</t>
+          <t>• 33/2017/TT-BTNMT — sửa đổi, bổ sung — hiệu lực 05/12/2017
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=125567
+• 27/2018/TT-BTNMT — bãi bỏ — hiệu lực 01/03/2019
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133433
+• 13/2019/TT-BTNMT — sửa đổi, bổ sung — hiệu lực 23/09/2019
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=137027
+• 09/2021/TT-BTNMT — sửa đổi, bổ sung — hiệu lực 01/09/2021
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=149005
+• 02/2023/TT-BTNMT — bãi bỏ — hiệu lực 20/05/2023
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=166137
+• 12/2024/TT-BTNMT — bãi bỏ — hiệu lực 01/08/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173538
+• 26/2024/TT-BTNMT — bãi bỏ — hiệu lực 15/01/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174271</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr"/>
@@ -2476,7 +2753,16 @@
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Quyết định số 32/2023/QĐ-TTg Bãi bỏ toàn bộ hoặc một phần một số văn bản quy phạm pháp luật của Thủ tướng Chính phủ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=166438) | bãi bỏ: Quyết định số 41/2026/QĐ-TTg Bãi bỏ một số văn bản quy phạm pháp luật của Thủ tướng Chính phủ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=4be348c0-9607-11f1-8d51-af7dccec1993) | bãi bỏ: Quyết định số 31/2015/QĐ-TTg Về định mức hành lý, tài sản di chuyển, quà biếu, quà tặng, hàng mẫu được miễn thuế, xét miễn thuế, không chịu  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=73839) | sửa đổi, bổ sung: Nghị định số 136/2007/NĐ-CP Về xuất cảnh, nhập cảnh của công dân Việt Nam (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=13615) | sửa đổi, bổ sung: Quyết định số 114/2001/QĐ-TTg Về việc sửa đổi, bổ sung một số điều của Quyết định số 210/1999/QĐ-TTg ngày 27 tháng 10 năm 1999 của Thủ tướng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=23253)</t>
+          <t>• 114/2001/QĐ-TTg — sửa đổi, bổ sung — hiệu lực 15/08/2001
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=23253
+• 136/2007/NĐ-CP — sửa đổi, bổ sung — hiệu lực 14/09/2007
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=13615
+• 31/2015/QĐ-TTg — bãi bỏ — hiệu lực 01/10/2015
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=73839
+• 32/2023/QĐ-TTg — bãi bỏ — hiệu lực 21/12/2023
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=166438
+• 41/2026/QĐ-TTg — bãi bỏ — hiệu lực 01/10/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=4be348c0-9607-11f1-8d51-af7dccec1993</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr"/>
@@ -2518,7 +2804,10 @@
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>đình chỉ thi hành: Nghị định số 203/2026/NĐ-CP Quy định về thi hành án tử hình bằng tiêm thuốc độc (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=aac7bf60-7d02-11f1-844e-e9d0ea08e798) | sửa đổi, bổ sung: Nghị định số 184/2025/NĐ-CP Quy định phân định thẩm quyền khi tổ chức chính quyền địa phương 02 cấp và sửa đổi, bổ sung một số điều của các  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179825)</t>
+          <t>• 184/2025/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179825
+• 203/2026/NĐ-CP — đình chỉ thi hành — hiệu lực 01/07/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=aac7bf60-7d02-11f1-844e-e9d0ea08e798</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr"/>
@@ -2560,7 +2849,8 @@
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 221/2013/NĐ-CP Quy định chế độ áp dụng biện pháp xử lý hành chính đưa vào cơ sở cai nghiện bắt buộc (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32938)</t>
+          <t>• 221/2013/NĐ-CP — bãi bỏ — hiệu lực 15/02/2014
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32938</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr"/>
@@ -2602,7 +2892,12 @@
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Thông tư số 07/2024/TT-BKHCN Sửa đổi, bổ sung một số điều tại các văn bản quy phạm pháp luật thuộc thẩm quyền của Bộ trưởng Bộ Khoa học và C (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=170642) | sửa đổi, bổ sung: Thông tư số 13/2023/TT-BKHCN Bãi bỏ một số văn bản quy phạm pháp luật do Bộ trưởng Bộ Khoa học và Công nghệ ban hành, liên tịch ban hành (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=162124) | thay thế: Thông tư số 54/2025/TT-BKHCN Quy định về hoạt động kiểm định, hiệu chuẩn, thử nghiệm phương tiện đo, chuẩn đo lường (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186195)</t>
+          <t>• 13/2023/TT-BKHCN — sửa đổi, bổ sung — hiệu lực 30/06/2023
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=162124
+• 07/2024/TT-BKHCN — sửa đổi, bổ sung — hiệu lực 22/11/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=170642
+• 54/2025/TT-BKHCN — thay thế — hiệu lực 15/02/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186195</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr"/>
@@ -2644,7 +2939,10 @@
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 11/VBHN-BXD Nghị định về xây dựng, quản lý, sử dụng nghĩa trang và cơ sở hỏa táng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=142413) | sửa đổi, bổ sung: Nghị định số 98/2019/NĐ-CP Sửa đổi, bổ sung một số điều của các nghị định thuộc lĩnh vực hạ tầng kỹ thuật (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=140187)</t>
+          <t>• 98/2019/NĐ-CP — sửa đổi, bổ sung — hiệu lực 15/02/2020
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=140187
+• 11/VBHN-BXD — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=142413</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr"/>
@@ -2686,7 +2984,24 @@
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 126/2020/NĐ-CP Quy định chi tiết một số điều của Luật Quản lý thuế (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=146459) | bãi bỏ: Nghị định số 181/2025/NĐ-CP Quy định chi tiết thi hành một số điều của Luật Thuế giá trị gia tăng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187347) | bãi bỏ: Nghị định số 360/2025/NĐ-CP Quy định chi tiết thi hành một số điều của Luật Thuế tiêu thụ đặc biệt (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186980) | hợp nhất: Văn bản hợp nhất số 31/VBHN-BTC Quy định chi tiết và hướng dẫn thi hành một số điều Luật Thuế giá trị gia tăng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=158225) | hợp nhất: Văn bản hợp nhất số 18/VBHN-BTC Quy định chi tiết và hướng dẫn thi hành một số Điều của Luật thuế tiêu thụ đặc biệt và Luật sửa đổi, bổ sung (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118407) | hợp nhất: Văn bản hợp nhất số 16/VBHN-BTC Quy định về xử phạt vi phạm hành chính lĩnh vực về thuế và cưỡng chế thi hành quyết định hành chính thuế (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118404) | hợp nhất: Văn bản hợp nhất số 17/VBHN-BTC Quy định chi tiết và hướng dẫn thi hành một số điều Luật Thuế giá trị gia tăng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118405) | hợp nhất: Văn bản hợp nhất số 19/VBHN-BTC Quy định chi tiết thi hành một số điều của Luật quản lý thuế và Luật sửa đổi, bổ sung một số điều của Luật q (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118408) | sửa đổi, bổ sung: Nghị định số 146/2017/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 100/2016/NĐ-CP ngày 01 tháng 7 năm 2016 và Nghị định số 12/2015/NĐ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=126410)</t>
+          <t>• 146/2017/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/02/2018
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=126410
+• 126/2020/NĐ-CP — bãi bỏ — hiệu lực 05/12/2020
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=146459
+• 181/2025/NĐ-CP — bãi bỏ — hiệu lực 01/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187347
+• 360/2025/NĐ-CP — bãi bỏ — hiệu lực 01/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186980
+• 16/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118404
+• 17/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118405
+• 18/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118407
+• 19/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118408
+• 31/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=158225</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr"/>
@@ -2728,7 +3043,8 @@
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 01/2019/TT-BXD Bãi bỏ toàn bộ hoặc một phần một số văn bản quy phạm pháp luật do Bộ trưởng Bộ Xây dựng ban hành hoặc liên tịch b (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=136228)</t>
+          <t>• 01/2019/TT-BXD — bãi bỏ — hiệu lực 15/08/2019
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=136228</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr"/>
@@ -2770,7 +3086,8 @@
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Thông tư số 16/2026/TT-BXD Hướng dẫn xác định và quản lý các chi phí liên quan đến việc xây dựng, điều chỉnh chương trình, kế hoạch phát tri (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=5f662d30-8e47-11f1-8158-c1fa247e8bd5)</t>
+          <t>• 16/2026/TT-BXD — sửa đổi, bổ sung — hiệu lực 29/04/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=5f662d30-8e47-11f1-8158-c1fa247e8bd5</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr"/>
@@ -2812,7 +3129,10 @@
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 74/2022/TT-BTC Quy định về hình thức, thời hạn thu, nộp, kê khai các khoản phí, lệ phí thuộc thẩm quyền quy định của Bộ Tài chín (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=158215) | sửa đổi, bổ sung: Thông tư số 06/2025/TT-BTC Sửa đổi, bổ sung một số điều của các Thông tư của Bộ trưởng Bộ Tài chính quy định về phí, lệ phí (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174853)</t>
+          <t>• 74/2022/TT-BTC — bãi bỏ — hiệu lực 22/12/2022
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=158215
+• 06/2025/TT-BTC — sửa đổi, bổ sung — hiệu lực 10/03/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174853</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr"/>
@@ -2854,7 +3174,8 @@
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>thay thế: Nghị định số 66/2014/NĐ-CP Quy định chi tiết, hướng dẫn thi hành một số điều của Luật Phòng, chống thiên tai (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=36766)</t>
+          <t>• 66/2014/NĐ-CP — thay thế — hiệu lực 20/08/2014
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=36766</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr"/>
@@ -2896,7 +3217,28 @@
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 31/VBHN-BTC Quy định chi tiết và hướng dẫn thi hành một số điều Luật Thuế giá trị gia tăng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=158225) | hợp nhất: Văn bản hợp nhất số 17/VBHN-BTC Quy định chi tiết và hướng dẫn thi hành một số điều Luật Thuế giá trị gia tăng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118405) | hợp nhất: Văn bản hợp nhất số 13/VBHN-BTC Quy định chi tiết và hướng dẫn thi hành một số điều Luật Thuế giá trị gia tăng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=67827) | sửa đổi, bổ sung: Nghị định số 91/2014/NĐ-CP Sửa đổi, bổ sung một số điều tại các Nghị định quy định về thuế (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=37143) | sửa đổi, bổ sung: Nghị định số 100/2016/NĐ-CP Quy định chi tiết và hướng dẫn thi hành một số điều của Luật sửa đổi, bổ sung một số điều của Luật thuế giá trị  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=112489) | sửa đổi, bổ sung: Nghị định số 49/2022/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 209/2013/NĐ-CP ngày 18 tháng 12 năm 2013 của Chính phủ quy định chi (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=155137) | sửa đổi, bổ sung: Nghị định số 146/2017/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 100/2016/NĐ-CP ngày 01 tháng 7 năm 2016 và Nghị định số 12/2015/NĐ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=126410) | sửa đổi, bổ sung: Nghị định số 12/2015/NĐ-CP Quy định chi tiết thi hành Luật sửa đổi, bổ sung một số điều của các Luật về thuế và sửa đổi, bổ sung một số điều (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=51578) | sửa đổi, bổ sung: Thông tư số 130/2016/TT-BTC Hướng dẫn thực hiện Nghị định số 100/2016/NĐ-CP ngày 01 tháng 7 năm 2016 của Chính phủ quy định chi tiết thi hàn (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118086) | sửa đổi, bổ sung: Nghị định số 10/2017/NĐ-CP Ban hành Quy chế quản lý tài chính của Tập đoàn Điện lực Việt Nam và sửa đổi, bổ sung khoản 4 Điều 4 Nghị định số (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=119077) | thay thế: Nghị định số 181/2025/NĐ-CP Quy định chi tiết thi hành một số điều của Luật Thuế giá trị gia tăng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187347)</t>
+          <t>• 91/2014/NĐ-CP — sửa đổi, bổ sung — hiệu lực 15/11/2014
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=37143
+• 12/2015/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/01/2015
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=51578
+• 100/2016/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/07/2016
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=112489
+• 130/2016/TT-BTC — sửa đổi, bổ sung — hiệu lực 01/07/2016
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118086
+• 10/2017/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/04/2017
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=119077
+• 146/2017/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/02/2018
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=126410
+• 49/2022/NĐ-CP — sửa đổi, bổ sung — hiệu lực 12/09/2022
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=155137
+• 181/2025/NĐ-CP — thay thế — hiệu lực 01/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187347
+• 13/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=67827
+• 17/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118405
+• 31/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=158225</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr"/>
@@ -2980,7 +3322,12 @@
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 16/VBHN-BTC Quy định chi tiết phạm vi địa bàn hoạt động hải quan; trách nhiệm phối hợp trong phòng, chống buôn lậu, vận  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=129036) | sửa đổi, bổ sung: Nghị định số 153/2026/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 01/2015/NĐ-CP ngày 02 tháng 01 năm 2015 của Chính phủ quy định chi (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=6f6eb4c0-7f30-11f1-87c0-45d4081ddc83) | sửa đổi, bổ sung: Nghị định số 12/2018/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 01/2015/NĐ-CP ngày 02 tháng 01 năm 2015 của Chính phủ quy định chi  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=128877)</t>
+          <t>• 12/2018/NĐ-CP — sửa đổi, bổ sung — hiệu lực 10/03/2018
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=128877
+• 153/2026/NĐ-CP — sửa đổi, bổ sung — hiệu lực 05/07/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=6f6eb4c0-7f30-11f1-87c0-45d4081ddc83
+• 16/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=129036</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr"/>
@@ -3022,7 +3369,10 @@
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 364/VBHN-BVHTTDL Nghị định (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=b14c2470-9bb1-11f1-90e8-e7dd3137bfa4) | sửa đổi, bổ sung: Nghị định số 129/2021/NĐ-CP sửa đổi, bổ sung một số điều của các Nghị định quy định xử phạt vi phạm hành chính trong lĩnh vực du lịch; thể t (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=155691)</t>
+          <t>• 129/2021/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/01/2022
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=155691
+• 364/VBHN-BVHTTDL — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=b14c2470-9bb1-11f1-90e8-e7dd3137bfa4</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr"/>
@@ -3064,7 +3414,14 @@
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 02/VBHN-BKHCN Quy định về xử phạt vi phạm hành chính trong lĩnh vực tiêu chuẩn, đo lường, chất lượng sản phẩm, hàng hóa (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=154195) | sửa đổi, bổ sung: Nghị định số 126/2021/NĐ-CP Sửa đổi, bổ sung một số điều của các nghị định quy định xử phạt vi phạm hành chính trong lĩnh vực sở hữu công ng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=154199) | sửa đổi, bổ sung: Nghị định số 42/2019/NĐ-CP Quy định xử phạt vi phạm hành chính trong lĩnh vực thủy sản (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135367) | sửa đổi, bổ sung: Nghị định số 106/2025/NĐ-CP Quy định xử phạt vi phạm hành chính trong lĩnh vực phòng cháy, chữa cháy và cứu nạn, cứu hộ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=177735)</t>
+          <t>• 42/2019/NĐ-CP — sửa đổi, bổ sung — hiệu lực 05/07/2019
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135367
+• 126/2021/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/01/2022
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=154199
+• 106/2025/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=177735
+• 02/VBHN-BKHCN — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=154195</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr"/>
@@ -3106,7 +3463,16 @@
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 40/2024/TT-BGTVT Quy định về công tác phòng, chống, khắc phục hậu quả thiên tai trong lĩnh vực đường bộ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174157) | sửa đổi, bổ sung: Thông tư số 25/2024/TT-BGTVT Sửa đổi, bổ sung một số điều của Thông tư số 50/2015/TT-BGTVT ngày 23 tháng 9 năm 2015 của Bộ trưởng Bộ Giao th (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=168214) | sửa đổi, bổ sung: Thông tư số 43/2021/TT-BGTVT Sửa đổi, bổ sung một số điều của Thông tư số 03/2019/TT-BGTVT ngày 11 tháng 01 năm 2019 của Bộ trưởng Bộ Giao t (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152588) | sửa đổi, bổ sung: Thông tư số 36/2020/TT-BGTVT Sửa đổi, bổ sung một số điều của các Thông tư quy định về chế độ báo cáo định kỳ trong lĩnh vực đường bộ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=145902) | sửa đổi, bổ sung: Thông tư số 22/2023/TT-BGTVT Sửa đổi, bổ sung một số điều của Thông tư số 03/2019/TT-BGTVT ngày 11 tháng 01 năm 2019 của Bộ trưởng Bộ Giao t (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=163042)</t>
+          <t>• 36/2020/TT-BGTVT — sửa đổi, bổ sung — hiệu lực 15/02/2021
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=145902
+• 43/2021/TT-BGTVT — sửa đổi, bổ sung — hiệu lực 01/03/2022
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152588
+• 22/2023/TT-BGTVT — sửa đổi, bổ sung — hiệu lực 15/08/2023
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=163042
+• 25/2024/TT-BGTVT — sửa đổi, bổ sung — hiệu lực 01/08/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=168214
+• 40/2024/TT-BGTVT — bãi bỏ — hiệu lực 01/01/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174157</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr"/>
@@ -3148,7 +3514,18 @@
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: LUẬT THI HÀNH TẠM GIỮ, TẠM GIAM VÀ CẤM ĐI KHỎI NƠI CƯ TRÚ SỐ 128/2025/QH15 (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186570) | sửa đổi, bổ sung: Luật Tư pháp người chưa thành niên số 59/2024/QH15 (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=175425) | sửa đổi, bổ sung: Luật Giám định tư pháp số 105/2025/QH15 (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187758) | sửa đổi, bổ sung: Luật sửa đổi, bổ sung một số điều của Bộ luật Tố tụng hình sự số 02/2021/QH15 (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=153151) | sửa đổi, bổ sung: Luật sửa đổi, bổ sung một số điều của Luật Hải quan số 11/2026/QH16 (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=9e4921a0-a2b1-11f1-8b6e-45ba51c9efb5) | sửa đổi, bổ sung: Luật Tổ chức Toà án nhân dân số số: 34/2024/QH15 (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=170570)</t>
+          <t>• Luật sửa đổi, bổ sung một số điều của Bộ luật Tố tụng hình sự số 02/2021/QH15 — sửa đổi, bổ sung — hiệu lực 01/12/2021
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=153151
+• Luật Tổ chức Toà án nhân dân số số: 34/2024/QH15 — sửa đổi, bổ sung — hiệu lực 01/01/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=170570
+• 59/2024/QH15 — sửa đổi, bổ sung — hiệu lực 01/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=175425
+• 105/2025/QH15 — sửa đổi, bổ sung — hiệu lực 01/05/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187758
+• LUẬT THI HÀNH TẠM GIỮ, TẠM GIAM VÀ CẤM ĐI KHỎI NƠI CƯ TRÚ SỐ 128/2025/QH15 — sửa đổi, bổ sung — hiệu lực 01/07/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186570
+• Luật sửa đổi, bổ sung một số điều của Luật Hải quan số 11/2026/QH16 — sửa đổi, bổ sung — hiệu lực 01/03/2027
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=9e4921a0-a2b1-11f1-8b6e-45ba51c9efb5</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr"/>
@@ -3190,7 +3567,10 @@
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 12/2025/TT-BTP Ban hành, hướng dẫn sử dụng, quản lý mẫu sổ quốc tịch và mẫu giấy tờ về quốc tịch (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186318) | hợp nhất: Văn bản hợp nhất số 4101/VBHN-BTP Ban hành, hướng dẫn sử dụng, quản lý mẫu sổ quốc tịch và mẫu giấy tờ về quốc tịch (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=169236)</t>
+          <t>• 12/2025/TT-BTP — bãi bỏ — hiệu lực 01/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186318
+• 4101/VBHN-BTP — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=169236</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr"/>
@@ -3232,7 +3612,8 @@
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>thay thế: Nghị định số 136/2006/NĐ-CP Quy định chi tiết và hướng dẫn thi hành một số điều của Luật Khiếu nại, tố cáo và các Luật sửa đổi, bổ sung một  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=14979)</t>
+          <t>• 136/2006/NĐ-CP — thay thế — hiệu lực 09/12/2006
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=14979</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr"/>
@@ -3274,7 +3655,10 @@
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Nghị định số 09/2005/NĐ-CP Về việc quy định xử phạt vi phạm hành chính trong lĩnh vực giao thông đường thuỷ nội địa (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=18507) | sửa đổi, bổ sung: Nghị định số 77/1998/NĐ-CP Về sửa đổi, bổ sung một số điều của Nghị định số 40/CP ngày 5/7/1996 của Chính phủ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=7469)</t>
+          <t>• 77/1998/NĐ-CP — sửa đổi, bổ sung — hiệu lực 11/10/1998
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=7469
+• 09/2005/NĐ-CP — sửa đổi, bổ sung — hiệu lực 24/02/2005
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=18507</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr"/>
@@ -3316,7 +3700,18 @@
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 06/VBHN-BTC Hướng dẫn thi hành một số điều của nghị định số 45/2007/NĐ-CP ngày 27 tháng 3 năm 2007 của Chính phủ quy địn (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=67761) | hợp nhất: Văn bản hợp nhất số 06/VBHN-BTC Hướng dẫn thi hành một số điều của Nghị định số 45/2007/NĐ-CP ngày 27 tháng 3 năm 2007 của Chính phủ quy địn (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111472) | sửa đổi, bổ sung: Thông tư số 124/2012/TT-BTC Hướng dẫn thi hành một số điều của Nghị định số 45/2007/NĐ-CP ngày 27 tháng 3 năm 2007 của Chính phủ quy định ch (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=67760) | sửa đổi, bổ sung: Thông tư số 194/2014/TT-BTC Sửa đổi, bổ sung một số điều của Thông tư số 124/2012/TT-BTC ngày 30/7/2012 của Bộ Tài chính hướng dẫn thi hành  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=67756) | thay thế: Thông tư số 50/2017/TT-BTC Hướng dẫn thi hành Nghị định số 73/2016/NĐ-CP ngày 01 tháng 7 năm 2016 của Chính phủ quy đinh chi tiết thi hành L (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=122601) | thay thế: Thông tư số 50/2017/TT-BTC Hướng dẫn thi hành Nghị định số 73/2016/NĐ-CP ngày 01 tháng 7 năm 2016 của Chính phủ quy định chi tiết thi hành L (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=122433)</t>
+          <t>• 124/2012/TT-BTC — sửa đổi, bổ sung — hiệu lực 01/10/2012
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=67760
+• 194/2014/TT-BTC — sửa đổi, bổ sung — hiệu lực 01/02/2015
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=67756
+• 50/2017/TT-BTC — thay thế — hiệu lực 01/07/2017
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=122433
+• 50/2017/TT-BTC — thay thế — hiệu lực 01/07/2017
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=122601
+• 06/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111472
+• 06/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=67761</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr"/>
@@ -3358,7 +3753,14 @@
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 09/VBHN-BTC Quy định xử phạt vi phạm hành chính trong lĩnh vực chứng khoán và thị trường chứng khoán (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=156570) | hợp nhất: Văn bản hợp nhất số 17/VBHN-BTC Nghị định số 156/2020/NĐ-CP Quy định xử phạt vi phạm hành chính trong lĩnh vực chứng khoán và thị trường chứ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=f69936f0-6937-11f1-a48d-29bc6b0fd706) | sửa đổi, bổ sung: Nghị định số 128/2021/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 156/2020/NĐ-CP ngày 31 tháng 12 năm 2020 của Chính phủ quy định xử (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152529) | sửa đổi, bổ sung: Nghị định số 306/2025/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 156/2020/NĐ-CP ngày 31 tháng 12 năm 2020 của Chính phủ quy định xử (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186388)</t>
+          <t>• 128/2021/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/01/2022
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152529
+• 306/2025/NĐ-CP — sửa đổi, bổ sung — hiệu lực 09/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186388
+• 09/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=156570
+• 17/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=f69936f0-6937-11f1-a48d-29bc6b0fd706</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr"/>
@@ -3400,7 +3802,10 @@
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Thông tư số 17/2023/TT-BGTVT Sửa đổi, bổ sung một số điều của Thông tư số 40/2016/TT-BGTVT ngày 7 tháng 12 năm 2016 của Bộ trưởng Bộ Giao th (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=161666) | sửa đổi, bổ sung: Thông tư số 16/2022/TT-BGTVT Sửa đổi, bổ sung một số điều của các Thông tư trong lĩnh vực đăng kiểm (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=154915)</t>
+          <t>• 16/2022/TT-BGTVT — sửa đổi, bổ sung — hiệu lực 15/08/2022
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=154915
+• 17/2023/TT-BGTVT — sửa đổi, bổ sung — hiệu lực 15/08/2023
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=161666</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr"/>
@@ -3442,7 +3847,10 @@
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 137/2024/NĐ-CP Quy định về giao dịch điện tử của cơ quan nhà nước và hệ thống thông tin phục vụ giao dịch điện tử (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=171147) | bãi bỏ: Nghị định số 47/2024/NĐ-CP Quy định về Danh mục Cơ sở dữ liệu quốc gia; việc xây dựng, cập nhật, duy trì, khai khác và sử dụng cơ sở dữ liệu (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=166966)</t>
+          <t>• 47/2024/NĐ-CP — bãi bỏ — hiệu lực 09/05/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=166966
+• 137/2024/NĐ-CP — bãi bỏ — hiệu lực 23/10/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=171147</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr"/>
@@ -3484,7 +3892,10 @@
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 07/2017/TT-BLĐTBXH Quy định chế độlàm việc của nhà giáo giáo dục nghề nghiệp (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=119515) | bãi bỏ: Thông tư số 08/2017/TT-BLĐTBXH Quy định chuẩn về chuyên môn, nghiệp vụ của nhà giáo giáo dục nghề nghiệp (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=119519)</t>
+          <t>• 08/2017/TT-BLĐTBXH — bãi bỏ — hiệu lực 01/05/2017
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=119519
+• 07/2017/TT-BLĐTBXH — bãi bỏ — hiệu lực 01/07/2017
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=119515</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr"/>
@@ -3526,7 +3937,10 @@
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 27/2019/TT-BLĐTBXH Ban hành danh mục thiết bị đào tạo tối thiểu trình độ trung cấp, trình độ cao đẳng cho một số nghề thuộc nhóm (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=141640) | bãi bỏ: Thông tư số 26/2019/TT-BLĐTBXH Ban hành danh mục thiết bị đào tạo tối thiểu trình độ trung cấp, trình độ cao đẳng cho một số nghề thuộc nhóm (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=141638)</t>
+          <t>• 26/2019/TT-BLĐTBXH — bãi bỏ — hiệu lực 09/02/2020
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=141638
+• 27/2019/TT-BLĐTBXH — bãi bỏ — hiệu lực 09/02/2020
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=141640</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr"/>
@@ -3568,7 +3982,8 @@
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 128/2013/TT-BTC Quy định về thủ tục hải quan; kiểm tra, giám sát hải quan; thuế xuất khẩu, thuế nhập khẩu và quản lý thuế đối vớ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32604) | thay thế: Thông tư số 128/2013/TT-BTC Quy định về thủ tục hải quan; kiểm tra, giám sát hải quan; thuế xuất khẩu, thuế nhập khẩu và quản lý thuế đối vớ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32604)</t>
+          <t>• 128/2013/TT-BTC — bãi bỏ, thay thế — hiệu lực 01/11/2013
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32604</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr"/>
@@ -3610,7 +4025,20 @@
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 34/VBHN-NHNN Quy định về phát hành kỳ phiếu, tín phiếu, chứng chỉ tiền gửi, trái phiếu trong nước của tổ chức tín dụng,  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111763) | hợp nhất: Văn bản hợp nhất số 14/VBHN-NHNN Quy định về phát hành kỳ phiếu, tín phiếu, chứng chỉ tiền gửi, trái phiếu trong nước của tổ chức tín dụng,  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=102033) | hợp nhất: Văn bản hợp nhất số 05/VBHN-NHNN Quy định về phát hành kỳ phiếu, tín phiếu, chứng chỉ tiền gửi, trái phiếu trong nước của tổ chức tín dụng,  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=140654) | sửa đổi, bổ sung: Thông tư số 16/2016/TT-NHNN Sửa đổi, bổ sung một số điều của Thông tư số 34/2013/TT-NHNN ngày 31 tháng 12 năm 2013 của Thống đốc Ngân hàng N (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111664) | sửa đổi, bổ sung: Thông tư số 29/2015/TT-NHNN Sửa đổi, bổ sung một số văn bản quy phạm pháp luật của Ngân hàng Nhà nước Việt Nam quy định về thành phần hồ sơ  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=96046) | sửa đổi, bổ sung: Thông tư số 33/2019/TT-NHNN Sửa đổi, bổ sung một số điều của Thông tư số 34/2013/TT-NHNN ngày 31 tháng 12 năm 2013 của Thống đốc Ngân hàng N (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=139893) | thay thế: Thông tư số 01/2021/TT-NHNN Quy định về phát hành kỳ phiếu, tín phiếu, chứng chỉ tiền gửi, trái phiếu trong nước của tổ chức tín dụng, chi n (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=147126)</t>
+          <t>• 29/2015/TT-NHNN — sửa đổi, bổ sung — hiệu lực 08/02/2016
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=96046
+• 16/2016/TT-NHNN — sửa đổi, bổ sung — hiệu lực 01/07/2016
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111664
+• 33/2019/TT-NHNN — sửa đổi, bổ sung — hiệu lực 19/02/2020
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=139893
+• 01/2021/TT-NHNN — thay thế — hiệu lực 17/05/2021
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=147126
+• 05/VBHN-NHNN — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=140654
+• 14/VBHN-NHNN — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=102033
+• 34/VBHN-NHNN — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111763</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr"/>
@@ -3652,7 +4080,16 @@
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 123/2015/NĐ-CP Quy định chi tiết một số điều và biện pháp thi hành Luật Hộ tịch (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=92897) | bãi bỏ: Nghị định số 19/2011/NĐ-CP Quy định chi tiết thi hành một số điều của Luật Nuôi con nuôi (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26222) | hợp nhất: Văn bản hợp nhất số 8013/VBHN-BTP Về đăng ký và quản lý hộ tịch (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32721) | hợp nhất: Văn bản hợp nhất số 8013/VBHN-BTP Về đăng ký và quản lý hộ tịch (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32948) | sửa đổi, bổ sung: Nghị định số 06/2012/NĐ-CP Sửa đổi, bổ sung một số điều của các Nghị định về hộ tịch, hôn nhân và gia đình và chứng thực (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=27159)</t>
+          <t>• 19/2011/NĐ-CP — bãi bỏ — hiệu lực 08/05/2011
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26222
+• 06/2012/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/04/2012
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=27159
+• 123/2015/NĐ-CP — bãi bỏ — hiệu lực 01/01/2016
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=92897
+• 8013/VBHN-BTP — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32721
+• 8013/VBHN-BTP — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32948</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr"/>
@@ -3694,7 +4131,22 @@
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 04/VBHN-BNNPTNT hợp nhất Thông tư quy định về kiểm tra, chứng nhận an toàn thực phẩm thủy sản xuất khẩu. (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=136878) | hợp nhất: Văn bản hợp nhất số 02/VBHN-BNNPTNT Quy định về kiểm tra, chứng nhận an toàn thực phẩm thủy sản xuất khẩu (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=159656) | hợp nhất: Văn bản hợp nhất số 32/VBHN-BNNPTNT Quy định về thẩm định, chứng nhận an toàn thực phẩm thủy sản xuất khẩu (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=172683) | sửa đổi, bổ sung: Thông tư số 02/2017/TT-BNNPTNT Sửa đổi, bổ sung một số điều tại thông tư số 48/2013/TT-BNNPTNT ngày 12/11/2013 quy định về kiểm tra, chứng n (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=122443) | sửa đổi, bổ sung: Thông tư số 16/2018/TT-BNNPTNT sửa đổi, bổ sung một số điều của Thông tư số 48/2013/TT-BNNPTNT ngày 12/11/2013 của Bộ trưởng Bộ Nông nghiệp  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=132279) | sửa đổi, bổ sung: Thông tư số 17/2025/TT-BNNMT Quy định về phân cấp quản lý nhà nước trong lĩnh vực quản lý chất lượng nông lâm sản và thủy sản (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178667) | sửa đổi, bổ sung: Thông tư số 17/2024/TT-BNNPTNT Sửa đổi, bổ sung một số Thông tư quy định thẩm định, chứng nhận cơ sở sản xuất, kinh doanh thực phẩm nông, lâ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=172685) | thay thế: Thông tư số 80/2025/TT-BNNMT Quy định về thẩm định, chứng nhận an toàn thực phẩm thủy sản xuất khẩu (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186338)</t>
+          <t>• 02/2017/TT-BNNPTNT — sửa đổi, bổ sung — hiệu lực 30/03/2017
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=122443
+• 16/2018/TT-BNNPTNT — sửa đổi, bổ sung — hiệu lực 13/12/2018
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=132279
+• 17/2024/TT-BNNPTNT — sửa đổi, bổ sung — hiệu lực 15/01/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=172685
+• 17/2025/TT-BNNMT — sửa đổi, bổ sung — hiệu lực 01/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178667
+• 80/2025/TT-BNNMT — thay thế — hiệu lực 02/02/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186338
+• 02/VBHN-BNNPTNT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=159656
+• 04/VBHN-BNNPTNT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=136878
+• 32/VBHN-BNNPTNT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=172683</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr"/>
@@ -3736,7 +4188,10 @@
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 118/2025/NĐ-CP Về thực hiện thủ tục hành chính theo cơ chế một cửa, một cửa liên thông tại Bộ phận Một cửa và Cổng Dịch vụ công (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178283) | sửa đổi, bổ sung: Nghị định số 107/2021/NĐ-CP Sửa đổi Nghị định 61/2018/NĐ-CP về thực hiện cơ chế một cửa, một cửa liên thông trong giải quyết thủ tục hành ch (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=162258)</t>
+          <t>• 107/2021/NĐ-CP — sửa đổi, bổ sung — hiệu lực 06/12/2021
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=162258
+• 118/2025/NĐ-CP — bãi bỏ — hiệu lực 01/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178283</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr"/>
@@ -3778,7 +4233,10 @@
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 40 /VBHN-BCT Thông tư Quy định điều độ, vận hành, thao tác, xử lý sự cố, khởi động đen và khôi phục hệ thống điện quốc g (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=180482) | sửa đổi, bổ sung: Thông tư số 46/2025/TT-BCT Sửa đổi, bổ sung một số điều của Thông tư số 04/2025/TT-BCT ngày 01 tháng 02 năm 2025 của Bộ trưởng Bộ Công Thươn (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=180486)</t>
+          <t>• 46/2025/TT-BCT — sửa đổi, bổ sung — hiệu lực 22/09/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=180486
+• Văn bản hợp nhất số 40 /VBHN-BCT Thông tư Quy định điều độ, vận hành, thao tác, xử lý sự c — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=180482</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr"/>
@@ -3820,7 +4278,8 @@
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Nghị định 69/2026/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 106/2025/NĐ-CP ngày 15 tháng 5 năm 2025 của Chính phủ quy định xử phạt (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=e23574c0-4c1e-11f1-b4dc-a19f4e8a4d2c)</t>
+          <t>• Nghị định 69/2026/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 106/2025/NĐ-CP ngày  — sửa đổi, bổ sung — hiệu lực 20/04/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=e23574c0-4c1e-11f1-b4dc-a19f4e8a4d2c</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr"/>
